--- a/Results/Two_Datasets_Assessment/Mushroom/Tables/fidelity_scores.xlsx
+++ b/Results/Two_Datasets_Assessment/Mushroom/Tables/fidelity_scores.xlsx
@@ -478,13 +478,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4593039257982813</v>
+        <v>0.5483620331151577</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3986959535889382</v>
+        <v>0.4233101009964155</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3697079075243822</v>
+        <v>0.5100652890254719</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4189129510429795</v>
+        <v>0.4217105291694392</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -532,13 +532,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3137404995245627</v>
+        <v>0.4937338788414433</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3242918599785742</v>
+        <v>0.4112404279912324</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -559,13 +559,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1712066308380989</v>
+        <v>0.2468983155019921</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1859964089934082</v>
+        <v>0.2390044671676202</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -586,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.343779489884602</v>
+        <v>0.4824131139296354</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4169179793197654</v>
+        <v>0.4626855436823677</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -613,13 +613,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4039431302146414</v>
+        <v>0.5099445363163269</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4473614274275943</v>
+        <v>0.4533921253521752</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5327151221325226</v>
+        <v>0.4794436099192703</v>
       </c>
       <c r="F8" t="n">
-        <v>0.48040030802591</v>
+        <v>0.4829562055483193</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -667,13 +667,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2754930305176135</v>
+        <v>0.2864860607661532</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2193952590882596</v>
+        <v>0.1849091874127333</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
